--- a/多元线性回归结果.xlsx
+++ b/多元线性回归结果.xlsx
@@ -8,18 +8,23 @@
   </bookViews>
   <sheets>
     <sheet name="清洗后数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="一元分析样本" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="一元分析汇总" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="一元回归系数" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="多元建模样本" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="逐步回归过程" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="模型比较" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="模型1系数" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="模型2系数" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="模型3系数" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="模型1VIF" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="模型2VIF" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="模型3VIF" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="相关系数矩阵" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="高相关变量样本" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="相关分析汇总" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="偏相关分析汇总" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="距离矩阵" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="一元回归样本" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="一元回归汇总" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="一元回归系数" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="多元建模样本" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="逐步回归过程" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="模型比较" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="模型1系数" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="模型2系数" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="模型3系数" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="模型1VIF" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="模型2VIF" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="模型3VIF" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1529,144 +1534,751 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>变量</t>
+          <t>y</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>系数</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>标准误</t>
+          <t>X2</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>t值</t>
+          <t>X3</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>p值</t>
+          <t>X4</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>下限95%</t>
+          <t>X5</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>上限95%</t>
+          <t>X6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>X7</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>const</t>
-        </is>
+      <c r="A2" t="n">
+        <v>5.3</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1763277311192453</v>
+        <v>5.1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2458011750058234</v>
+        <v>5.4</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7173591872173426</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4803752899050117</v>
+        <v>16.1</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3321507402064957</v>
+        <v>7.2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6848062024449862</v>
+        <v>4.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>48.1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>X2</t>
-        </is>
+      <c r="A3" t="n">
+        <v>5.2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7083873017487576</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03801168031564473</v>
+        <v>5.3</v>
       </c>
       <c r="D3" t="n">
-        <v>18.6360428127983</v>
+        <v>4.8</v>
       </c>
       <c r="E3" t="n">
-        <v>2.241878416704061e-15</v>
+        <v>16.3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6297541499789832</v>
+        <v>6.8</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7870204535185321</v>
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>48.3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>X3</t>
-        </is>
+      <c r="A4" t="n">
+        <v>5.1</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3127883241467359</v>
+        <v>5.1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03893651129413041</v>
+        <v>5.3</v>
       </c>
       <c r="D4" t="n">
-        <v>8.033290958809861</v>
+        <v>4.7</v>
       </c>
       <c r="E4" t="n">
-        <v>3.993931648343867e-08</v>
+        <v>16.5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2322420137349658</v>
+        <v>6.9</v>
       </c>
       <c r="G4" t="n">
-        <v>0.393334634558506</v>
+        <v>3.9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>48.6</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>X5</t>
-        </is>
+      <c r="A5" t="n">
+        <v>5.1</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.04023609828354946</v>
+        <v>5.1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01780204904150332</v>
+        <v>5.3</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.260194778126039</v>
+        <v>4.7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03358373702251093</v>
+        <v>16.9</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.07706244251430842</v>
+        <v>7.2</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.003409754052790495</v>
+        <v>3.8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H7" t="n">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H9" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H11" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>47.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H16" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E18" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E20" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H20" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H21" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E22" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E24" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="C27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E27" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H28" t="n">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1680,39 +2292,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>步骤</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>动作</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>变量</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>VIF</t>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>变量p值</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>当前变量</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>样本量</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>R²</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>调整R²</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>AIC</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>BIC</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>const</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1387.888888888805</v>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>加入</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.420989299558188e-10</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>27</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8049999999999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-82.16585083440003</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-79.57417710239137</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>X2</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.9999999999999998</v>
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>加入</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>X3</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.994658137223813e-07</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>X2, X3</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>27</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9405118763114555</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9355545326707435</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-111.1619090100901</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-107.2743984120771</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>加入</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>X5</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.03358373702251093</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>X2, X3, X5</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>27</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9513233435725145</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9449742144732772</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-114.5774909725825</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-109.3941435085652</v>
       </c>
     </row>
   </sheetData>
@@ -1726,49 +2472,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>变量</t>
+          <t>模型</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>VIF</t>
+          <t>自变量</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>样本量</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>R²</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>调整R²</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>AIC</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>BIC</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>F统计量</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>F检验p值</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>回归方程</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>const</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2223.071431125314</v>
+          <t>模型1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.8049999999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-82.16585083440003</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-79.57417710239137</v>
+      </c>
+      <c r="H2" t="n">
+        <v>108.3333333333333</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.420989299558188e-10</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>y = 1.3407 + 0.7222*X2</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>X2</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.012906224303744</v>
+          <t>模型2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>X2, X3</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9405118763114555</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9355545326707435</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-111.1619090100901</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-107.2743984120771</v>
+      </c>
+      <c r="H3" t="n">
+        <v>189.7209361456263</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.964098450434411e-15</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>y = 0.1691 + 0.6897*X2 + 0.2777*X3</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X3</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1.012906224303743</v>
+          <t>模型3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>X2, X3, X5</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>27</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9513233435725145</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9449742144732772</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-114.5774909725825</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-109.3941435085652</v>
+      </c>
+      <c r="H4" t="n">
+        <v>149.8352496386949</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.096044116010048e-15</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>y = 0.1763 + 0.7084*X2 + 0.3128*X3 - 0.0402*X5</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1782,6 +2652,486 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>下限95%</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>上限95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>const</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.340740740740735</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.3655797582891894</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.667437023906971</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.001157626165488057</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5878151344379174</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.093666347043552</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7222222222222228</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.06938886664887114</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10.40832999733066</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.420989299558188e-10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5793131762270152</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8651312682174304</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>下限95%</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>上限95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>const</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1691120565347413</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.2659869831449581</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6357907237986089</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5309293809351942</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.3798580953899153</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7180822084593979</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.6896547614791517</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.04014701839580707</v>
+      </c>
+      <c r="D3" t="n">
+        <v>17.17823113736334</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5.476362766522737e-15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6067953879583916</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7725141349999118</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>X3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.2776804547567133</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.03863933958864701</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.186469999562343</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.994658137223813e-07</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.197932777357448</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3574281321559787</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>标准误</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>t值</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>p值</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>下限95%</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>上限95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>const</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1763277311192453</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.2458011750058234</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.7173591872173426</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.4803752899050117</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.3321507402064957</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6848062024449862</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7083873017487576</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.03801168031564473</v>
+      </c>
+      <c r="D3" t="n">
+        <v>18.6360428127983</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.241878416704061e-15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6297541499789832</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7870204535185321</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>X3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.3127883241467359</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.03893651129413041</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8.033290958809861</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.993931648343867e-08</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2322420137349658</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.393334634558506</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>X5</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.04023609828354946</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.01780204904150332</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.260194778126039</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.03358373702251093</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.07706244251430842</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.003409754052790495</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>VIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>const</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1387.888888888805</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9999999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>VIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>const</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2223.071431125314</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.012906224303744</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>X3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.012906224303743</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1848,299 +3198,302 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>y</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>X3</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>X4</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>X5</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>X6</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>X7</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>5.3</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>48.1</v>
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5900799134605437</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8009735078044976</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.4333637458914178</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.455534511877175</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2658134224173345</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.554258567592101</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.4460487166625022</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>5.2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
       </c>
       <c r="B3" t="n">
-        <v>48.3</v>
+        <v>0.5900799134605437</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1431485555538703</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7792122247394991</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9171658644549293</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.4633487711139847</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.02110267091646345</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.06075547931478559</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>5.1</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
       </c>
       <c r="B4" t="n">
-        <v>48.6</v>
+        <v>0.8009735078044976</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1431485555538703</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.1340193521629748</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.04440260987616694</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2439091591407104</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4807166253343599</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.4376341423095708</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>5.1</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>X3</t>
+        </is>
       </c>
       <c r="B5" t="n">
-        <v>48.6</v>
+        <v>0.4333637458914178</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7792122247394991</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.1340193521629748</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6751048313794477</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4119455203104547</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3165208045158762</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.1846358647709343</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5.1</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>X4</t>
+        </is>
       </c>
       <c r="B6" t="n">
-        <v>48.4</v>
+        <v>0.455534511877175</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9171658644549293</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.04440260987616694</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6751048313794477</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.475838643273635</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.3261706885230025</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.01292295503971301</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>5.2</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>X5</t>
+        </is>
       </c>
       <c r="B7" t="n">
-        <v>48.6</v>
+        <v>0.2658134224173345</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.4633487711139847</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2439091591407104</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.4119455203104547</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.475838643273635</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.06325009730765285</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.4625483359360344</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>5.3</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>X6</t>
+        </is>
       </c>
       <c r="B8" t="n">
-        <v>48.5</v>
+        <v>0.554258567592101</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.02110267091646345</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4807166253343599</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.3165208045158762</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.3261706885230025</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.06325009730765285</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.605421089634206</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>5.2</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>X7</t>
+        </is>
       </c>
       <c r="B9" t="n">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" t="n">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" t="n">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="B12" t="n">
-        <v>48.3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="B13" t="n">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="B14" t="n">
-        <v>47.1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="B15" t="n">
-        <v>49.1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="B16" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" t="n">
-        <v>48.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>5</v>
-      </c>
-      <c r="B18" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="B19" t="n">
-        <v>48.8</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="B20" t="n">
-        <v>48.7</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="B21" t="n">
-        <v>48.7</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>5</v>
-      </c>
-      <c r="B22" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>5</v>
-      </c>
-      <c r="B23" t="n">
-        <v>48.7</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" t="n">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="B25" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="B26" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="B27" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="B28" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>5</v>
-      </c>
-      <c r="B29" t="n">
-        <v>48.9</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>5</v>
-      </c>
-      <c r="B30" t="n">
-        <v>48.7</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>5</v>
-      </c>
-      <c r="B31" t="n">
-        <v>48.8</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="B32" t="n">
-        <v>48.7</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="B33" t="n">
-        <v>48.7</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="B34" t="n">
-        <v>48.7</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="B35" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="B36" t="n">
-        <v>48.8</v>
+        <v>-0.4460487166625022</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.06075547931478559</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.4376341423095708</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.1846358647709343</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01292295503971301</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.4625483359360344</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.605421089634206</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2154,67 +3507,414 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>样本量</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>相关系数r</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>相关检验p值</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>R²</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>调整R²</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>截距</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>y系数</t>
+          <t>X4</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>35</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026年2月</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.4460487166625016</v>
+        <v>5.1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007238460555759935</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.1989594576362611</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.1746855018070569</v>
-      </c>
-      <c r="F2" t="n">
-        <v>55.65999999999997</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-1.375000000000004</v>
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026年1月</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025年12月</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025年11月</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025年10月</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025年9月</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025年8月</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025年7月</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025年6月</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025年5月</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025年4月</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025年3月</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025年2月</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025年1月</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2024年12月</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2024年11月</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2024年10月</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2024年9月</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2024年8月</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2024年7月</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2024年6月</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="C22" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2024年5月</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="C23" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2024年4月</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2024年3月</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2024年2月</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2024年1月</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="C27" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2023年12月</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2023年6月</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2023年5月</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023年4月</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>20.4</v>
       </c>
     </row>
   </sheetData>
@@ -2228,94 +3928,75 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>变量</t>
+          <t>x变量</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>系数</t>
+          <t>x变量含义</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>标准误</t>
+          <t>y变量</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>t值</t>
+          <t>y变量含义</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>p值</t>
+          <t>样本量</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>下限95%</t>
+          <t>Pearson相关系数</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>上限95%</t>
+          <t>相关检验p值</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>const</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>55.65999999999997</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2.470584262221512</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22.52908384915856</v>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>31个大城市城镇调查失业率</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>X4</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>全国城镇16—24岁劳动力失业率</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>1.305656938527614e-21</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
-        <v>50.63355852487271</v>
+        <v>0.9171658644549294</v>
       </c>
       <c r="G2" t="n">
-        <v>60.68644147512722</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>-1.375000000000004</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.480275776288813</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-2.862938478023821</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.007238460555759729</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-2.35212841385395</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-0.3978715861460572</v>
+        <v>1.050772167369258e-12</v>
       </c>
     </row>
   </sheetData>
@@ -2329,751 +4010,75 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>x变量</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>y变量</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>控制变量</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>控制变量含义</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>样本量</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>一阶偏相关系数</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>偏相关检验p值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>X1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>X2</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>X4</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>X3</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>X4</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>X5</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>X6</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>X7</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="B2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>全国城镇外来户籍劳动力失业率</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>16.1</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
-        <v>7.2</v>
+        <v>0.8507421417351633</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H2" t="n">
-        <v>48.1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H3" t="n">
-        <v>48.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="B4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H4" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E5" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H5" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E6" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H6" t="n">
-        <v>48.4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="B7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E7" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="F7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H7" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="B8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H8" t="n">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="B9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="C9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F9" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H9" t="n">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F10" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="F11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H11" t="n">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="B12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E12" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="F12" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H12" t="n">
-        <v>48.3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="B13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="C13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="F13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="B14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="C14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>5</v>
-      </c>
-      <c r="E14" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="F14" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="G14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>47.1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="B15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="G15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" t="n">
-        <v>49.1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E16" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="F16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H16" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H17" t="n">
-        <v>48.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>5</v>
-      </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E18" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H18" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="B19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E19" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F19" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H19" t="n">
-        <v>48.8</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="B20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="C20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E20" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F20" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H20" t="n">
-        <v>48.7</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="B21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="C21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="D21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H21" t="n">
-        <v>48.7</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>5</v>
-      </c>
-      <c r="B22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="C22" t="n">
-        <v>5</v>
-      </c>
-      <c r="D22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E22" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G22" t="n">
-        <v>4</v>
-      </c>
-      <c r="H22" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>5</v>
-      </c>
-      <c r="B23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="C23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E23" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G23" t="n">
-        <v>4</v>
-      </c>
-      <c r="H23" t="n">
-        <v>48.7</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" t="n">
-        <v>5</v>
-      </c>
-      <c r="C24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E24" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="F24" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>4</v>
-      </c>
-      <c r="H24" t="n">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="B25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="C25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="D25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="B26" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="C26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H26" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="B27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="C27" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="D27" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E27" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="F27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H27" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="D28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E28" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="F28" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="G28" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H28" t="n">
-        <v>49</v>
+        <v>2.613840146256215e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3087,173 +4092,3074 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:AE31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>步骤</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>动作</t>
+          <t>2026年2月</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>变量</t>
+          <t>2026年1月</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>变量p值</t>
+          <t>2025年12月</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>当前变量</t>
+          <t>2025年11月</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>样本量</t>
+          <t>2025年10月</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>R²</t>
+          <t>2025年9月</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>调整R²</t>
+          <t>2025年8月</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>AIC</t>
+          <t>2025年7月</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>2025年6月</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2025年5月</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2025年4月</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2025年3月</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>2025年2月</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>2025年1月</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>2024年12月</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>2024年11月</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>2024年10月</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>2024年9月</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>2024年8月</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>2024年7月</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>2024年6月</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>2024年5月</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>2024年4月</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>2024年3月</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>2024年2月</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>2024年1月</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>2023年12月</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>2023年6月</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>2023年5月</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>2023年4月</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026年2月</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.2236067977499782</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3999999999999986</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7999999999999972</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.603121954188138</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.807133769523637</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.702938636592639</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.603121954188141</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.204159457879231</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.4123105625617648</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.8062257748298522</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.412310562561768</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.004987562112089</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.716615541441224</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.019803902718557</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.906888370749729</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.910497317454282</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.403566884761822</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.513274595042157</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.204159457879231</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>5.215361924162118</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.716990566028302</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>4.318564576337834</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026年1月</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.2236067977499782</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2236067977499782</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6082762530298198</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.004987562112089</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.414213562373094</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.617250465660478</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.513274595042156</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.800000000000001</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5099019513592784</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.2828427124746186</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6324555320336739</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.2236067977499782</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.6000000000000014</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.30384048104053</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.531797780234433</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.8544003745317537</v>
+      </c>
+      <c r="V3" t="n">
+        <v>3.101612483854166</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.102379604162866</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.600000000000001</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.004987562112089</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.004987562112089</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.702938636592641</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5.024937810560445</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>4.527692569068709</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>4.130375285612675</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025年12月</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.3999999999999986</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2236067977499782</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3999999999999986</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.204159457879229</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.408318915758458</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.30384048104053</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.002498439450079</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.603121954188139</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6999999999999993</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1000000000000005</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4123105625617648</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.3999999999999986</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.8062257748298556</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.4123105625617646</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.6082762530298234</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.100000000000001</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.319482700948641</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.6324555320336773</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3.306055050963308</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.30867927612304</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.802775637731995</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.91049731745428</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.603121954188139</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.816637831516918</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>4.318564576337837</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>3.92045915678253</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025年11月</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.7999999999999972</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.6082762530298198</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3999999999999986</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4000000000000021</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8062257748298557</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.009975124224178</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9055385138137438</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.402082429892861</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.002498439450077</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.099999999999998</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.4123105625617648</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1000000000000005</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.7999999999999972</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.204159457879229</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.8062257748298521</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.2236067977499814</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.7000000000000028</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.923538406167137</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.2828427124746212</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3.70540146272978</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.707397274136176</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.202271554554523</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.599999999999998</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.599999999999998</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.308679276123038</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.002498439450077</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.418144406874906</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.920459156782534</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3.522782990761708</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025年10月</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.004987562112089</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.4000000000000021</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4123105625617648</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.612451549659708</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.5099019513592786</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.801785145224381</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.402082429892863</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.8062257748298557</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.4123105625617682</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.603121954188141</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.204159457879229</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.2236067977499782</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.529705854077836</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.2828427124746186</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4.10487515035476</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.106444913401814</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.601922366251539</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.707397274136178</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.402082429892863</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.019950248448356</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.522782990761708</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3.125699921617555</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025年9月</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.603121954188138</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.414213562373094</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.204159457879229</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8062257748298557</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4123105625617648</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.204159457879229</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.206243908376279</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.807133769523639</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.902629759044044</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.603121954188138</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.009975124224178</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.612451549659708</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.6324555320336739</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.1414213562373084</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.118033988749896</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.6082762530298198</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.509988913511872</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.512833614050059</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.006659275674582</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.402082429892861</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.402082429892861</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.114482300479487</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.807133769523639</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.61247837363769</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.114482300479489</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.716615541441224</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025年8月</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.807133769523637</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2.617250465660478</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.408318915758458</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.009975124224178</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.612451549659708</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.204159457879229</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.104536101718724</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.410215414239988</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.011234224026314</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.106444913401811</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.402082429892861</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.002498439450079</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.807133769523637</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.214031735997639</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.816025568065742</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.824828759089463</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.315294643796588</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.1414213562373084</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.799999999999997</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.714017850864661</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4.716990566028302</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.210700654285459</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.605551275463987</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.605551275463987</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.318564576337836</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4.011234224026314</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.408318915758461</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.910497317454282</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.513274595042156</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025年7月</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.702938636592639</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.513274595042156</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.30384048104053</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9055385138137438</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5099019513592786</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.104536101718724</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.306055050963308</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.906888370749727</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.002498439450079</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.300000000000001</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.9000000000000021</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.702938636592639</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.1095023109729</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.711724276862368</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.7280109889280512</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.2236067977499786</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.019803902718557</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.7071067811865468</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.609772228646445</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.61247837363769</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.106444913401815</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.501999200639361</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.501999200639361</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.21403173599764</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.906888370749727</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.512833614050059</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.014962686336267</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.617250465660478</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025年6月</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.603121954188141</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.800000000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.002498439450079</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.402082429892861</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.801785145224381</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.206243908376279</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.410215414239988</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.306055050963308</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.4000000000000004</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.30384048104053</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.009975124224178</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.408318915758458</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.603121954188141</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.600000000000001</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.600000000000001</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.101612483854166</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.318564576337837</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.617250465660482</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.30384048104053</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.3162277660168385</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.8062257748298556</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.8062257748298556</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.141421356237309</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.4000000000000004</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>6.818357573492315</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>6.319810123729985</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>5.921148537234983</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025年5月</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.204159457879231</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.603121954188139</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.002498439450077</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.402082429892863</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.807133769523639</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.011234224026314</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.906888370749727</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4000000000000004</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.905538513813742</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.61245154965971</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.009975124224176</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.204159457879231</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.7999999999999989</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.200000000000001</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.200000000000001</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.70185121722126</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.920459156782532</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.220360331117453</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.702938636592641</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.7071067811865486</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.2000000000000011</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4123105625617663</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.4123105625617663</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.3162277660168385</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>6.419501538281614</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>5.921148537234985</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>5.522680508593629</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025年4月</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.5099019513592784</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.6999999999999993</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.099999999999998</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.902629759044044</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.106444913401811</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.002498439450079</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.30384048104053</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.905538513813742</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.7071067811865469</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.104536101718724</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.1414213562373103</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.3162277660168385</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.30384048104053</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.800000000000001</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.014962686336267</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.315294643796591</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.607680962081061</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.612451549659711</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.104536101718727</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.216552506059645</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.905538513813742</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>5.514526271584895</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>5.015974481593781</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>4.617358552246076</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025年3月</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.4123105625617648</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.2828427124746186</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1000000000000005</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4123105625617648</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.8062257748298557</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.402082429892861</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.300000000000001</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.009975124224178</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.61245154965971</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.7071067811865469</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.3999999999999986</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.4123105625617648</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.8246211251235328</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4472135954999568</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.6324555320336773</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.104536101718727</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.30867927612304</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.6082762530298234</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3.313608305156179</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.319482700948641</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.811077027627484</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.204159457879229</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.204159457879229</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.923538406167135</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.61245154965971</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.80936586256442</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.310452412450462</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3.911521443121588</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025年2月</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.8062257748298522</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6324555320336739</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4123105625617648</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.1000000000000005</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.4123105625617682</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.002498439450079</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9000000000000021</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.408318915758458</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.009975124224176</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.104536101718724</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.3999999999999986</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.8062257748298522</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.216552506059643</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.8246211251235294</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.2828427124746212</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.7071067811865505</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.910497317454282</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.2236067977499814</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3.712142238654116</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.716615541441224</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.209072203437452</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.603121954188138</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.603121954188138</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.319482700948639</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.009975124224176</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.410215414239991</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.911521443121591</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>3.512833614050059</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025年1月</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.2236067977499782</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3999999999999986</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7999999999999972</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.603121954188138</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.807133769523637</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.702938636592639</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.603121954188141</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.204159457879231</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.4123105625617648</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.8062257748298522</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.412310562561768</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.004987562112089</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.716615541441224</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.019803902718557</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.906888370749729</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.910497317454282</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.403566884761822</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.513274595042157</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.204159457879231</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.215361924162118</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.716990566028302</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>4.318564576337834</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2024年12月</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.412310562561768</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6000000000000014</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.8062257748298556</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.204159457879229</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.603121954188141</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.009975124224178</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.214031735997639</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.1095023109729</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.7999999999999989</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1414213562373103</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.8246211251235328</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.216552506059643</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.412310562561768</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.4000000000000021</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.400000000000002</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.902629759044047</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.125699921617558</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.431782106327637</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2.501999200639361</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.503329637837291</v>
+      </c>
+      <c r="X16" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>加入</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>X2</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1.420989299558188e-10</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>X2</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>27</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.8049999999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-82.16585083440003</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-79.57417710239137</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="Y16" t="n">
+        <v>0.4123105625617646</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.4123105625617646</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.104536101718726</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.7999999999999989</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5.62227711874824</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>5.124451190127584</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>4.726520919238588</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2024年11月</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.4123105625617646</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8062257748298521</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.204159457879229</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.612451549659708</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.816025568065742</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.711724276862368</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.600000000000001</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.200000000000001</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.3162277660168385</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.4472135954999568</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.8246211251235294</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.4000000000000021</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.503329637837291</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.729468812791235</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.044030650891055</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.901723625709384</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.902629759044047</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.400000000000002</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.8062257748298556</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.8062257748298556</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.503329637837292</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.200000000000001</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>5.22398315464359</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.726520919238588</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>4.32897216438267</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2024年10月</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.004987562112089</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.6082762530298234</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.2236067977499814</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2236067977499782</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.6324555320336739</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.824828759089463</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.7280109889280512</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.600000000000001</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.200000000000001</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.30384048104053</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.6324555320336773</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.2828427124746212</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.004987562112089</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.400000000000002</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.5099019513592784</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.746424919657297</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.2999999999999998</v>
+      </c>
+      <c r="V18" t="n">
+        <v>3.901281840626234</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.901723625709384</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.400000000000002</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.802775637731995</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.802775637731995</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.501999200639363</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.200000000000001</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.22965719651132</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.733630940518893</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>3.337663853655724</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2024年9月</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.30384048104053</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.100000000000001</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7000000000000028</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.1414213562373084</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.315294643796588</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2236067977499786</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.101612483854166</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.70185121722126</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.800000000000001</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.104536101718727</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.7071067811865505</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.902629759044047</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.503329637837291</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.5099019513592784</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.236931687685298</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.5385164807134505</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.40454310910905</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.405877273185282</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.901723625709384</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.006659275674583</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.70185121722126</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.721558813185678</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.224903099319419</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.828427124746187</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2024年8月</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.716615541441224</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.531797780234433</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.319482700948641</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.923538406167137</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.529705854077836</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.118033988749896</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1414213562373084</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.019803902718557</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.318564576337837</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.920459156782532</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3.014962686336267</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.30867927612304</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.910497317454282</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.716615541441224</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.125699921617558</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.729468812791235</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.746424919657297</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.236931687685298</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.702938636592639</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.62227711874824</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4.627094120503711</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4.119465984809198</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>3.512833614050059</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.512833614050059</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.229657196511321</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3.920459156782532</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.501999200639361</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.002498439450079</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.603121954188138</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2024年7月</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.019803902718557</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.8544003745317537</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.6324555320336773</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.2828427124746212</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2828427124746186</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6082762530298198</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.799999999999997</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.7071067811865468</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.617250465660482</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.220360331117453</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.315294643796591</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.6082762530298234</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.2236067977499814</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.019803902718557</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.431782106327637</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.044030650891055</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.2999999999999998</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.5385164807134505</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.702938636592639</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>3.920459156782534</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.927456233660892</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.418677324489567</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.811077027627484</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.811077027627484</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.531797780234434</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.220360331117453</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.204759208325727</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.70540146272978</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>3.306055050963305</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2024年6月</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2.906888370749729</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.101612483854166</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.306055050963308</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.70540146272978</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4.10487515035476</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4.509988913511872</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5.714017850864661</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.609772228646445</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.30384048104053</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.702938636592641</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.607680962081061</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.313608305156179</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.712142238654116</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.906888370749729</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.501999200639361</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.901723625709384</v>
+      </c>
+      <c r="R22" t="n">
+        <v>3.901281840626234</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.40454310910905</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5.62227711874824</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3.920459156782534</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.503329637837291</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.1095023109729</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.1095023109729</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.702938636592641</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8.122191822408531</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>7.623647421018369</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>7.224956747275376</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2024年5月</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.910497317454282</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2.102379604162866</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.30867927612304</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.707397274136176</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.106444913401814</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.512833614050059</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.716990566028302</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.61247837363769</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.3162277660168385</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.7071067811865486</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.612451549659711</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.319482700948641</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.716615541441224</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.910497317454282</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.503329637837291</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.902629759044047</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.901723625709384</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.405877273185282</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4.627094120503711</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.927456233660892</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.5099019513592784</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.118033988749896</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.118033988749896</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.4000000000000004</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.7071067811865486</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.125307010929425</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>6.627216610312358</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>6.228964600958974</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2024年4月</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.403566884761822</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.600000000000001</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.802775637731995</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.202271554554523</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.601922366251539</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.006659275674582</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.210700654285459</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.106444913401815</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.2000000000000011</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.104536101718727</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.811077027627484</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.209072203437452</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.403566884761822</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.400000000000002</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.400000000000002</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.901723625709384</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4.119465984809198</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.418677324489567</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.503329637837291</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.5099019513592784</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.6082762530298234</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.6082762530298234</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.141421356237309</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.2000000000000011</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>6.618912297349167</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>6.120457499239744</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>5.721887800367987</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2024年3月</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.004987562112089</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.599999999999998</v>
+      </c>
+      <c r="F25" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>加入</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>X3</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1.994658137223813e-07</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>X2, X3</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>27</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.9405118763114555</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.9355545326707435</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-111.1619090100901</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-107.2743984120771</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>加入</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>X5</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0.03358373702251093</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>X2, X3, X5</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>27</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9513233435725145</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9449742144732772</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-114.5774909725825</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-109.3941435085652</v>
+      <c r="G25" t="n">
+        <v>2.402082429892861</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.605551275463987</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.501999200639361</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.8062257748298556</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.4123105625617663</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.204159457879229</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.603121954188138</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.4123105625617646</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.8062257748298556</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.802775637731995</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.512833614050059</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.811077027627484</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.1095023109729</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.118033988749896</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.6082762530298234</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.7280109889280527</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.4123105625617663</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>6.013318551349164</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>5.514526271584895</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>5.115662224971463</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2024年2月</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.004987562112089</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.599999999999998</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.402082429892861</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.605551275463987</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.501999200639361</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8062257748298556</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.4123105625617663</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.204159457879229</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.603121954188138</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.4123105625617646</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.8062257748298556</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.802775637731995</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.512833614050059</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.811077027627484</v>
+      </c>
+      <c r="V26" t="n">
+        <v>2.1095023109729</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.118033988749896</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.6082762530298234</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.7280109889280527</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.4123105625617663</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>6.013318551349164</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>5.514526271584895</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>5.115662224971463</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2024年1月</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.513274595042157</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.702938636592641</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.91049731745428</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.308679276123038</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.707397274136178</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.114482300479487</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.318564576337836</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.21403173599764</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.141421356237309</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.3162277660168385</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.216552506059645</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.923538406167135</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.319482700948639</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.513274595042157</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.104536101718726</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.503329637837292</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.501999200639363</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.006659275674583</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4.229657196511321</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.531797780234434</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.4000000000000004</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.141421356237309</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.7280109889280527</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.7280109889280527</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.3162277660168385</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>6.726812023536856</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>6.228964600958975</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>5.830951894845299</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2023年12月</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.204159457879231</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.603121954188139</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.002498439450077</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.402082429892863</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.807133769523639</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.011234224026314</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.906888370749727</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.4000000000000004</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.905538513813742</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.61245154965971</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.009975124224176</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.204159457879231</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.7999999999999989</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.200000000000001</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.200000000000001</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.70185121722126</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.920459156782532</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.220360331117453</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.702938636592641</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.7071067811865486</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.2000000000000011</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.4123105625617663</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.4123105625617663</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.3162277660168385</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>6.419501538281614</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>5.921148537234985</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>5.522680508593629</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2023年6月</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>5.215361924162118</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5.024937810560445</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4.816637831516918</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4.418144406874906</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.019950248448356</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.61247837363769</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.408318915758461</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3.512833614050059</v>
+      </c>
+      <c r="J29" t="n">
+        <v>6.818357573492315</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6.419501538281614</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5.514526271584895</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4.80936586256442</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4.410215414239991</v>
+      </c>
+      <c r="O29" t="n">
+        <v>5.215361924162118</v>
+      </c>
+      <c r="P29" t="n">
+        <v>5.62227711874824</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5.22398315464359</v>
+      </c>
+      <c r="R29" t="n">
+        <v>4.22965719651132</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.721558813185678</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.501999200639361</v>
+      </c>
+      <c r="U29" t="n">
+        <v>4.204759208325727</v>
+      </c>
+      <c r="V29" t="n">
+        <v>8.122191822408531</v>
+      </c>
+      <c r="W29" t="n">
+        <v>7.125307010929425</v>
+      </c>
+      <c r="X29" t="n">
+        <v>6.618912297349167</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>6.013318551349164</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>6.013318551349164</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>6.726812023536856</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>6.419501538281614</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.9000000000000021</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2023年5月</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4.716990566028302</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4.527692569068709</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4.318564576337837</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.920459156782534</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.522782990761708</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.114482300479489</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.910497317454282</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3.014962686336267</v>
+      </c>
+      <c r="J30" t="n">
+        <v>6.319810123729985</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5.921148537234985</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5.015974481593781</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4.310452412450462</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.911521443121591</v>
+      </c>
+      <c r="O30" t="n">
+        <v>4.716990566028302</v>
+      </c>
+      <c r="P30" t="n">
+        <v>5.124451190127584</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.726520919238588</v>
+      </c>
+      <c r="R30" t="n">
+        <v>3.733630940518893</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.224903099319419</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.002498439450079</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3.70540146272978</v>
+      </c>
+      <c r="V30" t="n">
+        <v>7.623647421018369</v>
+      </c>
+      <c r="W30" t="n">
+        <v>6.627216610312358</v>
+      </c>
+      <c r="X30" t="n">
+        <v>6.120457499239744</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>5.514526271584895</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5.514526271584895</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>6.228964600958975</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>5.921148537234985</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.4000000000000021</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023年4月</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4.318564576337834</v>
+      </c>
+      <c r="C31" t="n">
+        <v>4.130375285612675</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3.92045915678253</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.522782990761708</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.125699921617555</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.716615541441224</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.513274595042156</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.617250465660478</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5.921148537234983</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5.522680508593629</v>
+      </c>
+      <c r="L31" t="n">
+        <v>4.617358552246076</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.911521443121588</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.512833614050059</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4.318564576337834</v>
+      </c>
+      <c r="P31" t="n">
+        <v>4.726520919238588</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.32897216438267</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3.337663853655724</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.828427124746187</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.603121954188138</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3.306055050963305</v>
+      </c>
+      <c r="V31" t="n">
+        <v>7.224956747275376</v>
+      </c>
+      <c r="W31" t="n">
+        <v>6.228964600958974</v>
+      </c>
+      <c r="X31" t="n">
+        <v>5.721887800367987</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>5.115662224971463</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5.115662224971463</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>5.830951894845299</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>5.522680508593629</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.9000000000000021</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.4000000000000021</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3267,173 +7173,299 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>模型</t>
+          <t>y</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>自变量</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>样本量</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>R²</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>调整R²</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>AIC</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>BIC</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>F统计量</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>F检验p值</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>回归方程</t>
+          <t>X7</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>模型1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>X2</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>27</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.8049999999999999</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-82.16585083440003</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-79.57417710239137</v>
-      </c>
-      <c r="H2" t="n">
-        <v>108.3333333333333</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.420989299558188e-10</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>y = 1.3407 + 0.7222*X2</t>
-        </is>
+      <c r="A2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>48.1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>模型2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>X2, X3</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>27</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.9405118763114555</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.9355545326707435</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-111.1619090100901</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-107.2743984120771</v>
-      </c>
-      <c r="H3" t="n">
-        <v>189.7209361456263</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.964098450434411e-15</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>y = 0.1691 + 0.6897*X2 + 0.2777*X3</t>
-        </is>
+      <c r="A3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>48.3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>模型3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>X2, X3, X5</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>27</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.9513233435725145</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9449742144732772</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-114.5774909725825</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-109.3941435085652</v>
-      </c>
-      <c r="H4" t="n">
-        <v>149.8352496386949</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.096044116010048e-15</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>y = 0.1763 + 0.7084*X2 + 0.3128*X3 - 0.0402*X5</t>
-        </is>
+      <c r="A4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B7" t="n">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="B8" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B13" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="B14" t="n">
+        <v>47.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B15" t="n">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="B16" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" t="n">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="B19" t="n">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="B20" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B21" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B25" t="n">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="B26" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B27" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="B28" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" t="n">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" t="n">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B32" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="B33" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B34" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B35" t="n">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="B36" t="n">
+        <v>48.8</v>
       </c>
     </row>
   </sheetData>
@@ -3447,94 +7479,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>变量</t>
+          <t>样本量</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>系数</t>
+          <t>R²</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>标准误</t>
+          <t>调整R²</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>t值</t>
+          <t>截距</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>p值</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>下限95%</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>上限95%</t>
+          <t>y系数</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>const</t>
-        </is>
+      <c r="A2" t="n">
+        <v>35</v>
       </c>
       <c r="B2" t="n">
-        <v>1.340740740740735</v>
+        <v>0.1989594576362611</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3655797582891894</v>
+        <v>0.1746855018070569</v>
       </c>
       <c r="D2" t="n">
-        <v>3.667437023906971</v>
+        <v>55.65999999999997</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001157626165488057</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.5878151344379174</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2.093666347043552</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>X2</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.7222222222222228</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.06938886664887114</v>
-      </c>
-      <c r="D3" t="n">
-        <v>10.40832999733066</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.420989299558188e-10</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.5793131762270152</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.8651312682174304</v>
+        <v>-1.375000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -3548,7 +7537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3595,72 +7584,47 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1691120565347413</v>
+        <v>55.65999999999997</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2659869831449581</v>
+        <v>2.470584262221512</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6357907237986089</v>
+        <v>22.52908384915856</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5309293809351942</v>
+        <v>1.305656938527614e-21</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3798580953899153</v>
+        <v>50.63355852487271</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7180822084593979</v>
+        <v>60.68644147512722</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>X2</t>
+          <t>y</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6896547614791517</v>
+        <v>-1.375000000000004</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04014701839580707</v>
+        <v>0.480275776288813</v>
       </c>
       <c r="D3" t="n">
-        <v>17.17823113736334</v>
+        <v>-2.862938478023821</v>
       </c>
       <c r="E3" t="n">
-        <v>5.476362766522737e-15</v>
+        <v>0.007238460555759729</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6067953879583916</v>
+        <v>-2.35212841385395</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7725141349999118</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>X3</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.2776804547567133</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.03863933958864701</v>
-      </c>
-      <c r="D4" t="n">
-        <v>7.186469999562343</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.994658137223813e-07</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.197932777357448</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.3574281321559787</v>
+        <v>-0.3978715861460572</v>
       </c>
     </row>
   </sheetData>
